--- a/Testing Documentation/17092026-transmitter-testing.xlsx
+++ b/Testing Documentation/17092026-transmitter-testing.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucs-my.sharepoint.com/personal/rjparker128_tamu_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Testing Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{23C744D6-AA2F-4224-AA92-246D218904EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A8A0C287-B45C-4487-B119-59FCA22B938C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A8A0C287-B45C-4487-B119-59FCA22B938C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2690,15 +2690,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{964961A3-4153-4A97-872F-67A3E3E11555}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.5</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1.5</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>10.47</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2.5</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>10.77</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>11.03</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3.5</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>11.35</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>4</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>11.69</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4.5</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>12.02</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D12">
         <v>26</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>12.35</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D13">
         <v>27</v>
       </c>
